--- a/tresholds.xlsx
+++ b/tresholds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c64c0255ed6b9c45/Desktop/Diagnosis_System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="11_AD4DADEC636C813AC809E4C38859613C5ADEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19EAA551-F105-4A3A-9420-C23891E75DAA}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_AD4DADEC636C813AC809E4C38859613C5ADEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE17EE0-15A7-4444-8ADF-864B54C68E82}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>MSO 0</t>
   </si>
@@ -63,19 +63,37 @@
   </si>
   <si>
     <t>Sigma +3 odch std</t>
+  </si>
+  <si>
+    <t>STATYSTYKA</t>
+  </si>
+  <si>
+    <t>PAPER</t>
+  </si>
+  <si>
+    <t>Finetuning</t>
+  </si>
+  <si>
+    <t>Finetuning 23.02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,8 +116,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -115,6 +137,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,14 +406,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="4" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -401,101 +431,166 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>1496.7</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>1044.33</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>4.5000000000000003E-5</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>4.6999999999999997E-5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="H3">
+        <f>D3*0.95</f>
+        <v>4.2750000000000002E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>1260.8499999999999</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>682.97</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>2.1999999999999999E-5</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>2.5999999999999998E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <f>B2+B3</f>
+      <c r="B6">
+        <f>B3+B4</f>
         <v>2757.55</v>
       </c>
-      <c r="C5">
-        <f t="shared" ref="C5:E5" si="0">C2+C3</f>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="0">C3+C4</f>
         <v>1727.3</v>
       </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
+      <c r="D6">
+        <f>D3+D4</f>
         <v>6.7000000000000002E-5</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <f t="shared" si="0"/>
         <v>7.2999999999999999E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <f>B2+2*B3</f>
+      <c r="B7">
+        <f>B3+2*B4</f>
         <v>4018.3999999999996</v>
       </c>
-      <c r="C6">
-        <f t="shared" ref="C6:E6" si="1">C2+2*C3</f>
+      <c r="C7">
+        <f>C3+2*C4</f>
         <v>2410.27</v>
       </c>
-      <c r="D6">
-        <f t="shared" si="1"/>
+      <c r="D7">
+        <f>D3+2*D4</f>
         <v>8.8999999999999995E-5</v>
       </c>
-      <c r="E6">
-        <f t="shared" si="1"/>
+      <c r="E7">
+        <f>E3+2*E4</f>
         <v>9.8999999999999994E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f>B3+1.28*B4</f>
+        <v>3110.5879999999997</v>
+      </c>
+      <c r="C8">
+        <f>C3+2.75*C4</f>
+        <v>2922.4974999999999</v>
+      </c>
+      <c r="D8">
+        <f>D3</f>
+        <v>4.5000000000000003E-5</v>
+      </c>
+      <c r="E8">
+        <f>E3+0.9*E4</f>
+        <v>7.0400000000000004E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <f>B2+3*B3</f>
+      <c r="B9">
+        <f>B3+3*B4</f>
         <v>5279.25</v>
       </c>
-      <c r="C7">
-        <f t="shared" ref="C7:E7" si="2">C2+3*C3</f>
+      <c r="C9">
+        <f>C3+3*C4</f>
         <v>3093.24</v>
       </c>
-      <c r="D7">
-        <f t="shared" si="2"/>
-        <v>1.1100000000000001E-4</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="2"/>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f>E3+3*E4</f>
         <v>1.25E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
+        <v>1885.31</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1397.85</v>
+      </c>
+      <c r="D13" s="1">
+        <v>9.0000000000000006E-5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>6.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="2">
+        <v>5.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>6.9999999999999994E-5</v>
       </c>
     </row>
   </sheetData>

--- a/tresholds.xlsx
+++ b/tresholds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c64c0255ed6b9c45/Desktop/Diagnosis_System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="11_AD4DADEC636C813AC809E4C38859613C5ADEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE17EE0-15A7-4444-8ADF-864B54C68E82}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="11_AD4DADEC636C813AC809E4C38859613C5ADEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5CC60D8-5F72-405A-BD00-A1B48A7D4432}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>MSO 0</t>
   </si>
@@ -75,6 +75,21 @@
   </si>
   <si>
     <t>Finetuning 23.02</t>
+  </si>
+  <si>
+    <t>algorytm</t>
+  </si>
+  <si>
+    <t>2801.1176</t>
+  </si>
+  <si>
+    <t>1523.1193</t>
+  </si>
+  <si>
+    <t>0.0002</t>
+  </si>
+  <si>
+    <t>0.0001</t>
   </si>
 </sst>
 </file>
@@ -406,18 +421,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -431,12 +446,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -457,7 +472,7 @@
         <v>4.2750000000000002E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -474,7 +489,7 @@
         <v>2.5999999999999998E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -495,7 +510,7 @@
         <v>7.2999999999999999E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -516,7 +531,7 @@
         <v>9.8999999999999994E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8">
         <f>B3+1.28*B4</f>
         <v>3110.5879999999997</v>
@@ -534,7 +549,7 @@
         <v>7.0400000000000004E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -554,12 +569,12 @@
         <v>1.25E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>1885.31</v>
       </c>
@@ -573,24 +588,43 @@
         <v>6.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E19" s="2">
         <v>5.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E23">
         <v>6.9999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/tresholds.xlsx
+++ b/tresholds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c64c0255ed6b9c45/Desktop/Diagnosis_System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="11_AD4DADEC636C813AC809E4C38859613C5ADEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5CC60D8-5F72-405A-BD00-A1B48A7D4432}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="11_AD4DADEC636C813AC809E4C38859613C5ADEDD89" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E95338E5-D749-41DF-9FE2-1DB3ED44E0D8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>MSO 0</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>0.0001</t>
+  </si>
+  <si>
+    <t>najlepsze wyniki</t>
   </si>
 </sst>
 </file>
@@ -588,32 +591,32 @@
         <v>6.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E19" s="2">
         <v>5.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E23">
         <v>6.9999999999999994E-5</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>14</v>
       </c>
@@ -626,8 +629,12 @@
       <c r="E26" t="s">
         <v>17</v>
       </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>